--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,884 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127441987</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>805221</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7161477</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127441979</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91291</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>805284</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7161414</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127441986</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>805123</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7161468</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127441982</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91684</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>805186</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7161460</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127441981</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91684</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>805126</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7161411</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>S str</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127441977</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91291</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>805212</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7161374</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127441985</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>805220</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7161468</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127441984</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>805131</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7161408</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127441978</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91291</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>805222</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7161468</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127441986</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91684</v>
+        <v>91688</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91684</v>
+        <v>91688</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1668,6 +1668,1836 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127646881</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>805149</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7161401</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>hackat hål i gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127646904</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>805139</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7161392</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>hackat hål i granlåga</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127646639</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>805190</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7161390</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127647270</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>805125</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7161410</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>hack i granlåga</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127646710</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>805150</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7161397</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127647297</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91295</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>805124</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7161394</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127647071</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>805215</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7161475</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127647153</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>805186</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7161450</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>gammalt hack i liggande död gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127647280</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91295</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>805123</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7161408</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127647349</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>805136</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7161392</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>hack i granlåga</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127647292</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>805124</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7161394</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127647185</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>805133</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7161504</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>på död gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127646931</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>805222</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7161472</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127647321</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91295</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>805140</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7161379</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127647117</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>805192</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7161475</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127647096</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>805195</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7161479</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127647380</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91348</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kyan, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>805250</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7161380</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -1670,7 +1670,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127646881</v>
+        <v>127646904</v>
       </c>
       <c r="B12" t="n">
         <v>57658</v>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>805149</v>
+        <v>805139</v>
       </c>
       <c r="R12" t="n">
-        <v>7161401</v>
+        <v>7161392</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>hackat hål i gran</t>
+          <t>hackat hål i granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1780,7 +1780,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127646904</v>
+        <v>127646881</v>
       </c>
       <c r="B13" t="n">
         <v>57658</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>805139</v>
+        <v>805149</v>
       </c>
       <c r="R13" t="n">
-        <v>7161392</v>
+        <v>7161401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>hackat hål i granlåga</t>
+          <t>hackat hål i gran</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127647096</v>
+        <v>127647380</v>
       </c>
       <c r="B27" t="n">
-        <v>91326</v>
+        <v>91348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>805195</v>
+        <v>805250</v>
       </c>
       <c r="R27" t="n">
-        <v>7161479</v>
+        <v>7161380</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127647380</v>
+        <v>127647096</v>
       </c>
       <c r="B28" t="n">
-        <v>91348</v>
+        <v>91326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>805250</v>
+        <v>805195</v>
       </c>
       <c r="R28" t="n">
-        <v>7161380</v>
+        <v>7161479</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -2210,41 +2210,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647297</v>
+        <v>127647071</v>
       </c>
       <c r="B17" t="n">
-        <v>91295</v>
+        <v>57658</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2252,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>805124</v>
+        <v>805215</v>
       </c>
       <c r="R17" t="n">
-        <v>7161394</v>
+        <v>7161475</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,13 +2291,17 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2315,42 +2320,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127647071</v>
+        <v>127647297</v>
       </c>
       <c r="B18" t="n">
-        <v>57658</v>
+        <v>91295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2358,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805215</v>
+        <v>805124</v>
       </c>
       <c r="R18" t="n">
-        <v>7161475</v>
+        <v>7161394</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,17 +2400,13 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack i stående död gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127647292</v>
+        <v>127647185</v>
       </c>
       <c r="B22" t="n">
-        <v>57658</v>
+        <v>91348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,31 +2761,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2793,10 +2792,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>805124</v>
+        <v>805133</v>
       </c>
       <c r="R22" t="n">
-        <v>7161394</v>
+        <v>7161504</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,7 +2832,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>på död gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,6 +2841,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127647185</v>
+        <v>127647292</v>
       </c>
       <c r="B23" t="n">
-        <v>91348</v>
+        <v>57658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2871,30 +2871,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2902,10 +2903,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>805133</v>
+        <v>805124</v>
       </c>
       <c r="R23" t="n">
-        <v>7161504</v>
+        <v>7161394</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2942,7 +2943,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på död gran</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2951,7 +2952,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127441986</v>
       </c>
       <c r="B5" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127646904</v>
       </c>
       <c r="B12" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>127646881</v>
       </c>
       <c r="B13" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>127646639</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>127647270</v>
       </c>
       <c r="B15" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>127646710</v>
       </c>
       <c r="B16" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,42 +2210,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647071</v>
+        <v>127647297</v>
       </c>
       <c r="B17" t="n">
-        <v>57658</v>
+        <v>91297</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2253,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>805215</v>
+        <v>805124</v>
       </c>
       <c r="R17" t="n">
-        <v>7161475</v>
+        <v>7161394</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,17 +2290,13 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i stående död gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2320,41 +2315,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127647297</v>
+        <v>127647071</v>
       </c>
       <c r="B18" t="n">
-        <v>91295</v>
+        <v>57660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2362,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805124</v>
+        <v>805215</v>
       </c>
       <c r="R18" t="n">
-        <v>7161394</v>
+        <v>7161475</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,13 +2396,17 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>127647153</v>
       </c>
       <c r="B19" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>127647280</v>
       </c>
       <c r="B20" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>127647349</v>
       </c>
       <c r="B21" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>127647185</v>
       </c>
       <c r="B22" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>127647292</v>
       </c>
       <c r="B23" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>127646931</v>
       </c>
       <c r="B24" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>127647321</v>
       </c>
       <c r="B25" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>127647117</v>
       </c>
       <c r="B26" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127647380</v>
+        <v>127647096</v>
       </c>
       <c r="B27" t="n">
-        <v>91348</v>
+        <v>91328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>805250</v>
+        <v>805195</v>
       </c>
       <c r="R27" t="n">
-        <v>7161380</v>
+        <v>7161479</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127647096</v>
+        <v>127647380</v>
       </c>
       <c r="B28" t="n">
-        <v>91326</v>
+        <v>91350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>805195</v>
+        <v>805250</v>
       </c>
       <c r="R28" t="n">
-        <v>7161479</v>
+        <v>7161380</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -2210,41 +2210,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647297</v>
+        <v>127647071</v>
       </c>
       <c r="B17" t="n">
-        <v>91297</v>
+        <v>57660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2252,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>805124</v>
+        <v>805215</v>
       </c>
       <c r="R17" t="n">
-        <v>7161394</v>
+        <v>7161475</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,13 +2291,17 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2315,42 +2320,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127647071</v>
+        <v>127647297</v>
       </c>
       <c r="B18" t="n">
-        <v>57660</v>
+        <v>91297</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2358,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805215</v>
+        <v>805124</v>
       </c>
       <c r="R18" t="n">
-        <v>7161475</v>
+        <v>7161394</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,17 +2400,13 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack i stående död gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127647185</v>
+        <v>127647292</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>57660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,30 +2761,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2792,10 +2793,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>805133</v>
+        <v>805124</v>
       </c>
       <c r="R22" t="n">
-        <v>7161504</v>
+        <v>7161394</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2833,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på död gran</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2841,7 +2842,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127647292</v>
+        <v>127647185</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>91350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2871,31 +2871,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2903,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>805124</v>
+        <v>805133</v>
       </c>
       <c r="R23" t="n">
-        <v>7161394</v>
+        <v>7161504</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,7 +2942,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>på död gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2952,6 +2951,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -2210,42 +2210,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647071</v>
+        <v>127647297</v>
       </c>
       <c r="B17" t="n">
-        <v>57660</v>
+        <v>91297</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2253,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>805215</v>
+        <v>805124</v>
       </c>
       <c r="R17" t="n">
-        <v>7161475</v>
+        <v>7161394</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,17 +2290,13 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i stående död gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2320,41 +2315,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127647297</v>
+        <v>127647071</v>
       </c>
       <c r="B18" t="n">
-        <v>91297</v>
+        <v>57660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2362,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805124</v>
+        <v>805215</v>
       </c>
       <c r="R18" t="n">
-        <v>7161394</v>
+        <v>7161475</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,13 +2396,17 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127647292</v>
+        <v>127647185</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,31 +2761,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2793,10 +2792,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>805124</v>
+        <v>805133</v>
       </c>
       <c r="R22" t="n">
-        <v>7161394</v>
+        <v>7161504</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,7 +2832,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>på död gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,6 +2841,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127647185</v>
+        <v>127647292</v>
       </c>
       <c r="B23" t="n">
-        <v>91350</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2871,30 +2871,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2902,10 +2903,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>805133</v>
+        <v>805124</v>
       </c>
       <c r="R23" t="n">
-        <v>7161504</v>
+        <v>7161394</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2942,7 +2943,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på död gran</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2951,7 +2952,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127646904</v>
+        <v>127646881</v>
       </c>
       <c r="B12" t="n">
         <v>57660</v>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>805139</v>
+        <v>805149</v>
       </c>
       <c r="R12" t="n">
-        <v>7161392</v>
+        <v>7161401</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>hackat hål i granlåga</t>
+          <t>hackat hål i gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1780,7 +1780,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127646881</v>
+        <v>127646904</v>
       </c>
       <c r="B13" t="n">
         <v>57660</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>805149</v>
+        <v>805139</v>
       </c>
       <c r="R13" t="n">
-        <v>7161401</v>
+        <v>7161392</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>hackat hål i gran</t>
+          <t>hackat hål i granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1893,7 +1893,7 @@
         <v>127646639</v>
       </c>
       <c r="B14" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>127646710</v>
       </c>
       <c r="B16" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>127647297</v>
       </c>
       <c r="B17" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>127647280</v>
       </c>
       <c r="B20" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127647185</v>
+        <v>127647292</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>57660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,30 +2761,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2792,10 +2793,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>805133</v>
+        <v>805124</v>
       </c>
       <c r="R22" t="n">
-        <v>7161504</v>
+        <v>7161394</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2833,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på död gran</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2841,7 +2842,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127647292</v>
+        <v>127647185</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>91356</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2871,31 +2871,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2903,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>805124</v>
+        <v>805133</v>
       </c>
       <c r="R23" t="n">
-        <v>7161394</v>
+        <v>7161504</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,7 +2942,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>på död gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2952,6 +2951,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>127647321</v>
       </c>
       <c r="B25" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>127647117</v>
       </c>
       <c r="B26" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>127647096</v>
       </c>
       <c r="B27" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>127647380</v>
       </c>
       <c r="B28" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127441986</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127646881</v>
+        <v>127646904</v>
       </c>
       <c r="B12" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>805149</v>
+        <v>805139</v>
       </c>
       <c r="R12" t="n">
-        <v>7161401</v>
+        <v>7161392</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>hackat hål i gran</t>
+          <t>hackat hål i granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127646904</v>
+        <v>127646881</v>
       </c>
       <c r="B13" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>805139</v>
+        <v>805149</v>
       </c>
       <c r="R13" t="n">
-        <v>7161392</v>
+        <v>7161401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>hackat hål i granlåga</t>
+          <t>hackat hål i gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1893,7 +1893,7 @@
         <v>127646639</v>
       </c>
       <c r="B14" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>127647270</v>
       </c>
       <c r="B15" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>127646710</v>
       </c>
       <c r="B16" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,41 +2210,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647297</v>
+        <v>127647071</v>
       </c>
       <c r="B17" t="n">
-        <v>91303</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2252,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>805124</v>
+        <v>805215</v>
       </c>
       <c r="R17" t="n">
-        <v>7161394</v>
+        <v>7161475</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,13 +2291,17 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2315,42 +2320,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127647071</v>
+        <v>127647297</v>
       </c>
       <c r="B18" t="n">
-        <v>57660</v>
+        <v>91306</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2358,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805215</v>
+        <v>805124</v>
       </c>
       <c r="R18" t="n">
-        <v>7161475</v>
+        <v>7161394</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,17 +2400,13 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack i stående död gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>127647153</v>
       </c>
       <c r="B19" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>127647280</v>
       </c>
       <c r="B20" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>127647349</v>
       </c>
       <c r="B21" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127647292</v>
+        <v>127647185</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>91359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,31 +2761,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2793,10 +2792,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>805124</v>
+        <v>805133</v>
       </c>
       <c r="R22" t="n">
-        <v>7161394</v>
+        <v>7161504</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,7 +2832,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>på död gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,6 +2841,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127647185</v>
+        <v>127647292</v>
       </c>
       <c r="B23" t="n">
-        <v>91356</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2871,30 +2871,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2902,10 +2903,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>805133</v>
+        <v>805124</v>
       </c>
       <c r="R23" t="n">
-        <v>7161504</v>
+        <v>7161394</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2942,7 +2943,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på död gran</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2951,7 +2952,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>127646931</v>
       </c>
       <c r="B24" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>127647321</v>
       </c>
       <c r="B25" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>127647117</v>
       </c>
       <c r="B26" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127647096</v>
+        <v>127647380</v>
       </c>
       <c r="B27" t="n">
-        <v>91334</v>
+        <v>91359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>805195</v>
+        <v>805250</v>
       </c>
       <c r="R27" t="n">
-        <v>7161479</v>
+        <v>7161380</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127647380</v>
+        <v>127647096</v>
       </c>
       <c r="B28" t="n">
-        <v>91356</v>
+        <v>91337</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>805250</v>
+        <v>805195</v>
       </c>
       <c r="R28" t="n">
-        <v>7161380</v>
+        <v>7161479</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127441986</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>127646904</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>127646881</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>127646639</v>
       </c>
       <c r="B14" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>127647270</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>127646710</v>
       </c>
       <c r="B16" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,42 +2210,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647071</v>
+        <v>127647297</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>91314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2253,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>805215</v>
+        <v>805124</v>
       </c>
       <c r="R17" t="n">
-        <v>7161475</v>
+        <v>7161394</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,17 +2290,13 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i stående död gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2320,41 +2315,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127647297</v>
+        <v>127647071</v>
       </c>
       <c r="B18" t="n">
-        <v>91306</v>
+        <v>57669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2362,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805124</v>
+        <v>805215</v>
       </c>
       <c r="R18" t="n">
-        <v>7161394</v>
+        <v>7161475</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,13 +2396,17 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>127647153</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>127647280</v>
       </c>
       <c r="B20" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>127647349</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>127647185</v>
       </c>
       <c r="B22" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>127647292</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>127646931</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>127647321</v>
       </c>
       <c r="B25" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>127647117</v>
       </c>
       <c r="B26" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127647380</v>
+        <v>127647096</v>
       </c>
       <c r="B27" t="n">
-        <v>91359</v>
+        <v>91345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>805250</v>
+        <v>805195</v>
       </c>
       <c r="R27" t="n">
-        <v>7161380</v>
+        <v>7161479</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127647096</v>
+        <v>127647380</v>
       </c>
       <c r="B28" t="n">
-        <v>91337</v>
+        <v>91367</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>805195</v>
+        <v>805250</v>
       </c>
       <c r="R28" t="n">
-        <v>7161479</v>
+        <v>7161380</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91707</v>
+        <v>91708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91707</v>
+        <v>91708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>127646639</v>
       </c>
       <c r="B14" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>127646710</v>
       </c>
       <c r="B16" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,41 +2210,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647297</v>
+        <v>127647071</v>
       </c>
       <c r="B17" t="n">
-        <v>91314</v>
+        <v>57669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2252,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>805124</v>
+        <v>805215</v>
       </c>
       <c r="R17" t="n">
-        <v>7161394</v>
+        <v>7161475</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,13 +2291,17 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2315,42 +2320,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127647071</v>
+        <v>127647297</v>
       </c>
       <c r="B18" t="n">
-        <v>57669</v>
+        <v>91315</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2358,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805215</v>
+        <v>805124</v>
       </c>
       <c r="R18" t="n">
-        <v>7161475</v>
+        <v>7161394</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,17 +2400,13 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack i stående död gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>127647280</v>
       </c>
       <c r="B20" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127647185</v>
+        <v>127647292</v>
       </c>
       <c r="B22" t="n">
-        <v>91367</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,30 +2761,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2792,10 +2793,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>805133</v>
+        <v>805124</v>
       </c>
       <c r="R22" t="n">
-        <v>7161504</v>
+        <v>7161394</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2833,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på död gran</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2841,7 +2842,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127647292</v>
+        <v>127647185</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>91368</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2871,31 +2871,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2903,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>805124</v>
+        <v>805133</v>
       </c>
       <c r="R23" t="n">
-        <v>7161394</v>
+        <v>7161504</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,7 +2942,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>på död gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2952,6 +2951,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>127647321</v>
       </c>
       <c r="B25" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>127647117</v>
       </c>
       <c r="B26" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127647096</v>
+        <v>127647380</v>
       </c>
       <c r="B27" t="n">
-        <v>91345</v>
+        <v>91368</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>805195</v>
+        <v>805250</v>
       </c>
       <c r="R27" t="n">
-        <v>7161479</v>
+        <v>7161380</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127647380</v>
+        <v>127647096</v>
       </c>
       <c r="B28" t="n">
-        <v>91367</v>
+        <v>91346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>805250</v>
+        <v>805195</v>
       </c>
       <c r="R28" t="n">
-        <v>7161380</v>
+        <v>7161479</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127647292</v>
+        <v>127647185</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>91368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,31 +2761,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2793,10 +2792,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>805124</v>
+        <v>805133</v>
       </c>
       <c r="R22" t="n">
-        <v>7161394</v>
+        <v>7161504</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,7 +2832,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>på död gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,6 +2841,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127647185</v>
+        <v>127647292</v>
       </c>
       <c r="B23" t="n">
-        <v>91368</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2871,30 +2871,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2902,10 +2903,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>805133</v>
+        <v>805124</v>
       </c>
       <c r="R23" t="n">
-        <v>7161504</v>
+        <v>7161394</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2942,7 +2943,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på död gran</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2951,7 +2952,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127647380</v>
+        <v>127647096</v>
       </c>
       <c r="B27" t="n">
-        <v>91368</v>
+        <v>91346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>805250</v>
+        <v>805195</v>
       </c>
       <c r="R27" t="n">
-        <v>7161380</v>
+        <v>7161479</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127647096</v>
+        <v>127647380</v>
       </c>
       <c r="B28" t="n">
-        <v>91346</v>
+        <v>91368</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>805195</v>
+        <v>805250</v>
       </c>
       <c r="R28" t="n">
-        <v>7161479</v>
+        <v>7161380</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91708</v>
+        <v>91709</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91708</v>
+        <v>91709</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>127646639</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>127646710</v>
       </c>
       <c r="B16" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2210,42 +2210,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647071</v>
+        <v>127647297</v>
       </c>
       <c r="B17" t="n">
-        <v>57669</v>
+        <v>91316</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2253,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>805215</v>
+        <v>805124</v>
       </c>
       <c r="R17" t="n">
-        <v>7161475</v>
+        <v>7161394</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,17 +2290,13 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i stående död gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2320,41 +2315,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127647297</v>
+        <v>127647071</v>
       </c>
       <c r="B18" t="n">
-        <v>91315</v>
+        <v>57669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2362,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805124</v>
+        <v>805215</v>
       </c>
       <c r="R18" t="n">
-        <v>7161394</v>
+        <v>7161475</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,13 +2396,17 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>127647280</v>
       </c>
       <c r="B20" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>127647185</v>
       </c>
       <c r="B22" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>127647321</v>
       </c>
       <c r="B25" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>127647117</v>
       </c>
       <c r="B26" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127647096</v>
+        <v>127647380</v>
       </c>
       <c r="B27" t="n">
-        <v>91346</v>
+        <v>91369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>805195</v>
+        <v>805250</v>
       </c>
       <c r="R27" t="n">
-        <v>7161479</v>
+        <v>7161380</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127647380</v>
+        <v>127647096</v>
       </c>
       <c r="B28" t="n">
-        <v>91368</v>
+        <v>91347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>805250</v>
+        <v>805195</v>
       </c>
       <c r="R28" t="n">
-        <v>7161380</v>
+        <v>7161479</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>127646639</v>
       </c>
       <c r="B14" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>127646710</v>
       </c>
       <c r="B16" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>127647297</v>
       </c>
       <c r="B17" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>127647280</v>
       </c>
       <c r="B20" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>127647185</v>
       </c>
       <c r="B22" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>127647321</v>
       </c>
       <c r="B25" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>127647117</v>
       </c>
       <c r="B26" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127647380</v>
+        <v>127647096</v>
       </c>
       <c r="B27" t="n">
-        <v>91369</v>
+        <v>91348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,21 +3301,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>805250</v>
+        <v>805195</v>
       </c>
       <c r="R27" t="n">
-        <v>7161380</v>
+        <v>7161479</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,10 +3395,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127647096</v>
+        <v>127647380</v>
       </c>
       <c r="B28" t="n">
-        <v>91347</v>
+        <v>91370</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3406,21 +3406,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>805195</v>
+        <v>805250</v>
       </c>
       <c r="R28" t="n">
-        <v>7161479</v>
+        <v>7161380</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127441979</v>
+        <v>127441986</v>
       </c>
       <c r="B4" t="n">
-        <v>91317</v>
+        <v>57832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>805284</v>
+        <v>805123</v>
       </c>
       <c r="R4" t="n">
-        <v>7161414</v>
+        <v>7161468</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127441986</v>
+        <v>127441979</v>
       </c>
       <c r="B5" t="n">
-        <v>57832</v>
+        <v>91317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>805123</v>
+        <v>805284</v>
       </c>
       <c r="R5" t="n">
-        <v>7161468</v>
+        <v>7161414</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2210,41 +2210,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647297</v>
+        <v>127647071</v>
       </c>
       <c r="B17" t="n">
-        <v>91317</v>
+        <v>57669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2252,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>805124</v>
+        <v>805215</v>
       </c>
       <c r="R17" t="n">
-        <v>7161394</v>
+        <v>7161475</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,13 +2291,17 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2315,42 +2320,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127647071</v>
+        <v>127647297</v>
       </c>
       <c r="B18" t="n">
-        <v>57669</v>
+        <v>91317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2358,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805215</v>
+        <v>805124</v>
       </c>
       <c r="R18" t="n">
-        <v>7161475</v>
+        <v>7161394</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,17 +2400,13 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack i stående död gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -2210,42 +2210,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647071</v>
+        <v>127647297</v>
       </c>
       <c r="B17" t="n">
-        <v>57669</v>
+        <v>91317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2253,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>805215</v>
+        <v>805124</v>
       </c>
       <c r="R17" t="n">
-        <v>7161475</v>
+        <v>7161394</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,17 +2290,13 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i stående död gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2320,41 +2315,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127647297</v>
+        <v>127647071</v>
       </c>
       <c r="B18" t="n">
-        <v>91317</v>
+        <v>57669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2362,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805124</v>
+        <v>805215</v>
       </c>
       <c r="R18" t="n">
-        <v>7161394</v>
+        <v>7161475</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,13 +2396,17 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127647185</v>
+        <v>127647292</v>
       </c>
       <c r="B22" t="n">
-        <v>91370</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,30 +2761,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2792,10 +2793,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>805133</v>
+        <v>805124</v>
       </c>
       <c r="R22" t="n">
-        <v>7161504</v>
+        <v>7161394</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2833,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på död gran</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2841,7 +2842,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127647292</v>
+        <v>127647185</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>91370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2871,31 +2871,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2903,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>805124</v>
+        <v>805133</v>
       </c>
       <c r="R23" t="n">
-        <v>7161394</v>
+        <v>7161504</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,7 +2942,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>på död gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2952,6 +2951,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127441986</v>
+        <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>91317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>805123</v>
+        <v>805284</v>
       </c>
       <c r="R4" t="n">
-        <v>7161468</v>
+        <v>7161414</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127441979</v>
+        <v>127441986</v>
       </c>
       <c r="B5" t="n">
-        <v>91317</v>
+        <v>57832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>805284</v>
+        <v>805123</v>
       </c>
       <c r="R5" t="n">
-        <v>7161414</v>
+        <v>7161468</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2210,41 +2210,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647297</v>
+        <v>127647071</v>
       </c>
       <c r="B17" t="n">
-        <v>91317</v>
+        <v>57669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2252,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>805124</v>
+        <v>805215</v>
       </c>
       <c r="R17" t="n">
-        <v>7161394</v>
+        <v>7161475</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,13 +2291,17 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2315,42 +2320,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127647071</v>
+        <v>127647297</v>
       </c>
       <c r="B18" t="n">
-        <v>57669</v>
+        <v>91317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2358,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805215</v>
+        <v>805124</v>
       </c>
       <c r="R18" t="n">
-        <v>7161475</v>
+        <v>7161394</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,17 +2400,13 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack i stående död gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127647292</v>
+        <v>127647185</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>91370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,31 +2761,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2793,10 +2792,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>805124</v>
+        <v>805133</v>
       </c>
       <c r="R22" t="n">
-        <v>7161394</v>
+        <v>7161504</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,7 +2832,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>på död gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2842,6 +2841,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127647185</v>
+        <v>127647292</v>
       </c>
       <c r="B23" t="n">
-        <v>91370</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2871,30 +2871,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2902,10 +2903,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>805133</v>
+        <v>805124</v>
       </c>
       <c r="R23" t="n">
-        <v>7161504</v>
+        <v>7161394</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2942,7 +2943,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på död gran</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2951,7 +2952,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -2210,41 +2210,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647297</v>
+        <v>127647071</v>
       </c>
       <c r="B17" t="n">
-        <v>91317</v>
+        <v>57669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2252,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>805124</v>
+        <v>805215</v>
       </c>
       <c r="R17" t="n">
-        <v>7161394</v>
+        <v>7161475</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,13 +2291,17 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2315,42 +2320,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127647071</v>
+        <v>127647297</v>
       </c>
       <c r="B18" t="n">
-        <v>57669</v>
+        <v>91317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2358,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805215</v>
+        <v>805124</v>
       </c>
       <c r="R18" t="n">
-        <v>7161475</v>
+        <v>7161394</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2396,17 +2400,13 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack i stående död gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -2210,42 +2210,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127647071</v>
+        <v>127647297</v>
       </c>
       <c r="B17" t="n">
-        <v>57669</v>
+        <v>91317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2253,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>805215</v>
+        <v>805124</v>
       </c>
       <c r="R17" t="n">
-        <v>7161475</v>
+        <v>7161394</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,17 +2290,13 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hack i stående död gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2320,41 +2315,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127647297</v>
+        <v>127647071</v>
       </c>
       <c r="B18" t="n">
-        <v>91317</v>
+        <v>57669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2362,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>805124</v>
+        <v>805215</v>
       </c>
       <c r="R18" t="n">
-        <v>7161394</v>
+        <v>7161475</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,13 +2396,17 @@
           <t>2025-08-08</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hack i stående död gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98387</v>
+        <v>98549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,14 +885,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91317</v>
+        <v>91469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,14 +986,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127441986</v>
       </c>
       <c r="B5" t="n">
-        <v>57832</v>
+        <v>57876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,14 +1087,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91710</v>
+        <v>91862</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,14 +1188,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91710</v>
+        <v>91862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,14 +1294,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91317</v>
+        <v>91469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,14 +1395,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91352</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,14 +1496,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91352</v>
+        <v>91504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,14 +1597,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91317</v>
+        <v>91469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,7 +1698,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98549</v>
+        <v>98553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>127441986</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98553</v>
+        <v>98560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>127441986</v>
       </c>
       <c r="B5" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>127441986</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98586</v>
+        <v>98593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98593</v>
+        <v>98595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>127441986</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98595</v>
+        <v>98621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98621</v>
+        <v>98622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98622</v>
+        <v>98623</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98623</v>
+        <v>98627</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91911</v>
+        <v>91914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91911</v>
+        <v>91914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98627</v>
+        <v>98629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91914</v>
+        <v>91916</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91914</v>
+        <v>91916</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22441-2025 artfynd.xlsx
+++ b/artfynd/A 22441-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>127441987</v>
       </c>
       <c r="B3" t="n">
-        <v>98629</v>
+        <v>98633</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127441979</v>
       </c>
       <c r="B4" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127441982</v>
       </c>
       <c r="B6" t="n">
-        <v>91916</v>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>127441981</v>
       </c>
       <c r="B7" t="n">
-        <v>91916</v>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>127441977</v>
       </c>
       <c r="B8" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127441985</v>
       </c>
       <c r="B9" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>127441984</v>
       </c>
       <c r="B10" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>127441978</v>
       </c>
       <c r="B11" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
